--- a/conductas_micro.xlsx
+++ b/conductas_micro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\losaa\Downloads\Escritorio\Conductas Micro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA60B3A-2F7C-40C7-8373-11B6B5B51174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9E6118-35FA-4C1C-AC70-FC417B686279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38490" yWindow="-4840" windowWidth="19380" windowHeight="20970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="P1" sheetId="2" r:id="rId1"/>
@@ -1725,7 +1725,7 @@
     <col min="4" max="4" width="13.6328125" customWidth="1"/>
     <col min="8" max="8" width="6.90625" customWidth="1"/>
     <col min="9" max="9" width="7" customWidth="1"/>
-    <col min="10" max="10" width="12.6328125" customWidth="1"/>
+    <col min="10" max="11" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.35">
@@ -1799,7 +1799,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="174" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" ht="116" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="174" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" ht="116" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="174" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" ht="116" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -2139,7 +2139,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="174" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" ht="116" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="174" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" ht="116" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>23</v>
       </c>

--- a/conductas_micro.xlsx
+++ b/conductas_micro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\losaa\Downloads\Escritorio\Conductas Micro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9E6118-35FA-4C1C-AC70-FC417B686279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{055281AA-8ECA-411E-916A-B73E5EC23092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38490" yWindow="-4840" windowWidth="19380" windowHeight="20970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="P1" sheetId="2" r:id="rId1"/>

--- a/conductas_micro.xlsx
+++ b/conductas_micro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\losaa\Downloads\Escritorio\Conductas Micro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF7614B-FB39-48A8-B924-719E73BC9439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD02BA3-7B5D-4998-8297-AA833DADF3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19290" yWindow="-4840" windowWidth="19380" windowHeight="20970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/conductas_micro.xlsx
+++ b/conductas_micro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\losaa\Downloads\Escritorio\Conductas Micro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD02BA3-7B5D-4998-8297-AA833DADF3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04BDECD-8F6A-4988-80C6-DE965C0265C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19290" yWindow="-4840" windowWidth="19380" windowHeight="20970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="273">
   <si>
     <t>Conducta</t>
   </si>
@@ -361,9 +361,6 @@
     <t>IF</t>
   </si>
   <si>
-    <t>Evitar finalización/Impedir progresión (prioridad: portería)</t>
-  </si>
-  <si>
     <t>P9/P10/P7/P11</t>
   </si>
   <si>
@@ -421,9 +418,6 @@
     <t>https://youtu.be/6lFZeWFcY8c</t>
   </si>
   <si>
-    <t>Falta</t>
-  </si>
-  <si>
     <t>P4/P5/P6</t>
   </si>
   <si>
@@ -518,6 +512,345 @@
   </si>
   <si>
     <t>No robo + te superan → progresión limpia.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/G1DtGXwwwBY</t>
+  </si>
+  <si>
+    <t>Defensa 1c1 - Frecuencia de pasos</t>
+  </si>
+  <si>
+    <t>Defensa 1c1 - No cruzar carrera</t>
+  </si>
+  <si>
+    <t>Frenada de retorno</t>
+  </si>
+  <si>
+    <t>Incomodar al rival en balón largo</t>
+  </si>
+  <si>
+    <t>Ir al suelo</t>
+  </si>
+  <si>
+    <t>Meter cuerpo entre rival y balón</t>
+  </si>
+  <si>
+    <t>Orientar hacie fuera</t>
+  </si>
+  <si>
+    <t>Perseguir</t>
+  </si>
+  <si>
+    <t>Saltar a receptor</t>
+  </si>
+  <si>
+    <t>Defensa 1c1 - Bajar centro de gravedad</t>
+  </si>
+  <si>
+    <t>Defensa 1c1 - Brazo distancia</t>
+  </si>
+  <si>
+    <t>Defensa 1c1 - Uso funcional del brazo</t>
+  </si>
+  <si>
+    <t>https://youtu.be/EfVRM0Kq-Va</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Wg7aI4TtuPA</t>
+  </si>
+  <si>
+    <t>https://youtu.be/4uf6Uo2e_-s</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Ri-ZUJCuXeY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fX4gDM3zKh8</t>
+  </si>
+  <si>
+    <t>https://youtu.be/B_-N3l_ht2Q</t>
+  </si>
+  <si>
+    <t>https://youtu.be/RtKSK2Ab1dw</t>
+  </si>
+  <si>
+    <t>https://youtu.be/AKmu1zaNJmU</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7FDnvzZScjc</t>
+  </si>
+  <si>
+    <t>https://youtu.be/lA27BjEOnro</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ex392EfRm7s</t>
+  </si>
+  <si>
+    <t>https://youtu.be/bkSS86Xyz8g</t>
+  </si>
+  <si>
+    <t>https://youtu.be/UvBftEZpVZ8</t>
+  </si>
+  <si>
+    <t>https://youtu.be/zvQXP7Q2gMg</t>
+  </si>
+  <si>
+    <t>Dividir con 1er paso / cambio de ritmo</t>
+  </si>
+  <si>
+    <t>Rival con balón vivo y espacio para acelerar; tú en distancia de contención</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instante previo al toque/1er paso del rival (micro-tiempo). </t>
+  </si>
+  <si>
+    <t>Pasos cortos + base activa para frenar “sin pasarte” y quedar listo para reacelerar/entrar si aparece ventana.</t>
+  </si>
+  <si>
+    <t>Pasos cortos y rápidos (no zancada); CdG bajo-controlado; split step justo antes del toque; freno en 1–2 apoyos sin clavar; primer paso vivo para reacelerar o entrar con pierna cercana.</t>
+  </si>
+  <si>
+    <t>E1: zancada amplia → te pasas de frenada. E2: te clavas/te quedas “sentado”.</t>
+  </si>
+  <si>
+    <t>No puedes reacelerar ni entrar; recorte + progresión / falta.</t>
+  </si>
+  <si>
+    <t>Cambio de dirección + acelerar</t>
+  </si>
+  <si>
+    <t>Rival de frente con opción de acelerar a tu espalda</t>
+  </si>
+  <si>
+    <t>Micro-tiempo de giro/cambio.</t>
+  </si>
+  <si>
+    <t>Cadera disponible + reajustes sin cruzar para conservar opción de carrera.</t>
+  </si>
+  <si>
+    <t>Cadera abierta a la amenaza; reajustes laterales/diagonales sin cruzar; micro-freno 1–2 apoyos; primer paso vivo.</t>
+  </si>
+  <si>
+    <t>E1: cruzas cadera/pies → te bloqueas. E2: giras tarde.</t>
+  </si>
+  <si>
+    <t>Te ganan espalda / falta / ruptura.</t>
+  </si>
+  <si>
+    <t>Conducir/encarar</t>
+  </si>
+  <si>
+    <t>1v1 con espacio a tu espalda o a un lado; rival orientado a acelerar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuando arma 1er paso/cambio de ritmo. </t>
+  </si>
+  <si>
+    <t>Bajar CdG + base activa para frenar–girar–reacelerar sin perder línea.</t>
+  </si>
+  <si>
+    <t>CdG bajo sin colapso; pies activos; micro-frenos; primer paso disponible (drop/hip turn) según amenaza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E1: entras alto y te clavas. E2: colapsas rodilla/cadera. </t>
+  </si>
+  <si>
+    <t>Te aceleran / falta / línea rota.</t>
+  </si>
+  <si>
+    <t>Evitar finalización/Impedir progresión</t>
+  </si>
+  <si>
+    <t>Atraer + dividir</t>
+  </si>
+  <si>
+    <t>Rival aún sin contacto; amenaza de 1er paso.</t>
+  </si>
+  <si>
+    <t>Cuando ajustas sin “morder”</t>
+  </si>
+  <si>
+    <t>Distancia jugable para temporizar y atacar solo con ventana.</t>
+  </si>
+  <si>
+    <t>Pasos cortos; brazo guía sin tocar; semiperfil; split step justo antes del toque del rival.</t>
+  </si>
+  <si>
+    <t>E1: te pegas (te eliminan). E2: te alejas (gana metros/decide).</t>
+  </si>
+  <si>
+    <t>Progresión / pase / tiro frontal.</t>
+  </si>
+  <si>
+    <t>Conducir + proteger balón</t>
+  </si>
+  <si>
+    <t>Contacto probable; rival busca fijarte para girar/soltar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuando entra en tu radio de contacto. </t>
+  </si>
+  <si>
+    <t>Brazo corto como referencia sin empujar ni abrir codos.</t>
+  </si>
+  <si>
+    <t>Brazo corto y pegado; contacto en hombro/pecho; mano no lidera; base estable (no perder pies).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E1: brazo largo → falta. E2: sin brazo → te desplazan. </t>
+  </si>
+  <si>
+    <t>Falta / te giran / pierdes línea interior.</t>
+  </si>
+  <si>
+    <t>Balón largo a P9 (apoyo/descarga)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balón largo llega a P9 (control/recepción) y se activa descarga a cara (P8/P10) o giro si recibe con ventaja. </t>
+  </si>
+  <si>
+    <t>Si llegas con timing y contacto legal, limitas control/orientación del P9 y ralentizas la descarga.</t>
+  </si>
+  <si>
+    <t>Aproximación en diagonal a “hombro–pecho” (sin agarrar), meter cuerpo entre rival y balón cuando se separa, y/o meter pie cercano si el control se alarga.</t>
+  </si>
+  <si>
+    <t>Escaneo balón–P9–apoyos; llegada con pasos cortos + micro-freno; semi-perfil protegiendo tu espalda; contacto legal con antebrazo/hombro (sin empujar); pies activos para meter pie cercano si el balón se separa; si no hay opción de robo, orientar descarga hacia atrás/lateral y reubicar.</t>
+  </si>
+  <si>
+    <t>E1: llegas tarde/sin contacto → P9 controla y descarga limpio (o gira). E2: contacto excesivo (empujas/agarras) → falta peligrosa.</t>
+  </si>
+  <si>
+    <t>Progresión tras descarga / 2ª jugada rival / falta en zona crítica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distancia 1–2 m + rival expone balón (control largo) o aparece línea directa (pase/tiro) + sin opción de temporizar. </t>
+  </si>
+  <si>
+    <t>E1: decides tarde (sin ventana) → falta/penalti/roja. E2: entras cruzado o con pierna alejada</t>
+  </si>
+  <si>
+    <t>Recuperar / Impedir progresión</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z1–Z2 </t>
+  </si>
+  <si>
+    <t>Proteger balón y continuar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balón queda disputable (toque largo, control imperfecto, rebote) y llegas a igualar la acción. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuando entras a radio de contacto y puedes ganar la línea balón–rival antes del siguiente toque. </t>
+  </si>
+  <si>
+    <t>Interpones el cuerpo para proteger el balón, forzas que el rival pierda acceso limpio y aseguras la recuperación (control/pase simple) o falta a favor.</t>
+  </si>
+  <si>
+    <t>Semiperfil para “cerrar” la línea; base ancha y CdG bajo; hombro/cadera primero (no brazos); brazo de referencia legal para sentir al rival; pies activos (no cruzar); si hay contacto, absorbes y mantienes equilibrio; tras proteger, 1º toque jugable o pase seguro a apoyo cercano.</t>
+  </si>
+  <si>
+    <t>E1: llegas de lado y no ganas la línea (el rival mete pie). E2: usas brazos/agarre o pierdes base y te empujan.</t>
+  </si>
+  <si>
+    <t>Pérdida de balón, falta en contra o continuidad rival.</t>
+  </si>
+  <si>
+    <t>P6/P8/P10</t>
+  </si>
+  <si>
+    <t>Acelerar/dividir o filtrar</t>
+  </si>
+  <si>
+    <t>Vienes en retorno tras pase/superación y el poseedor rival tiene opción de progresar en conducción o filtrar</t>
+  </si>
+  <si>
+    <t>Si frenas con control, llegas “a tiempo” sin romperte ni ser eliminado</t>
+  </si>
+  <si>
+    <t>Ajustar distancia y velocidad con frenada progresiva para sostener eje, proteger intervalo y estar listo para temporizar/entrar si aparece ventana.</t>
+  </si>
+  <si>
+    <t>Pasos cortos (alta frecuencia) al llegar; CdG bajo-móvil; tronco estable; frenada en 1–2 apoyos finales (sin clavarte); pies activos (sin cruzar); cadera preparada para micro-giro/reaceleración; brazos equilibran. Sensación: “llego con freno y con primer paso disponible”.</t>
+  </si>
+  <si>
+    <t>E1: llegas pasado (frenas tarde / zancada larga) → te superan fácil. E2: te clavas (freno brusco) → no puedes reacelerar ni entrar</t>
+  </si>
+  <si>
+    <t>Conducción limpia / pase interior o ruptura / línea se parte</t>
+  </si>
+  <si>
+    <t>Impedir progresión/Impedir finalización</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transición con rival conduciendo en CC, espacio por delante y riesgo de tiro/pase final. </t>
+  </si>
+  <si>
+    <t>Cuando el poseedor aún no tiene línea directa de finalización (distancia de tiro no inmediata) y tú llegas a distancia de contención.</t>
+  </si>
+  <si>
+    <t>Temporizar y orientar su conducción hacia CI/CE (no permitir continuidad en CC),  a pierna no hábil, ganando tiempo para ayudas y reduciendo opciones de tiro/pase final.</t>
+  </si>
+  <si>
+    <t>Atacar portería en transición</t>
+  </si>
+  <si>
+    <t>Llegada con ritmo controlado + frenada 1–2 apoyos; semiperfil “cerrando CC”; CdG bajo; pasos cortos (sin cruzar); distancia jugable (ni clavar ni morder); brazo corto legal como referencia; si cambia ritmo: split-step y reaceleración corta; si intenta volver a CC: micro-reajuste para re-negar.</t>
+  </si>
+  <si>
+    <t>E1: temporizas demasiado pasivo y le dejas tiro/pase en CC. E2: muerdes sin ventaja y te recorta.</t>
+  </si>
+  <si>
+    <t>Finalización en CC o ruptura directa.</t>
+  </si>
+  <si>
+    <t>P7/P11/P9/P10</t>
+  </si>
+  <si>
+    <t>Atacar espacio en conducción</t>
+  </si>
+  <si>
+    <t>Rival supera primera presión y gana metros; tú quedas a “distancia de persecución” con posibilidad real de emparejar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuando igualas altura (paralelo/costado) y el balón se expone (toque largo / balón fuera del pie / cambio de ritmo). </t>
+  </si>
+  <si>
+    <t>Perseguir con trayectoria útil para emparejar y, según ventana, meter cuerpo, pinchar con pierna cercana o condicionar la conducción hacia zona menos dañina hasta que llegue ayuda.</t>
+  </si>
+  <si>
+    <t>Carrera controlada (no sobrepasar); semiperfil hombro–cadera a la línea de carrera; brazos legales para equilibrio/sensor; preparar frenada reactiva para entrar al balón; si hay ventana: entrada con pierna cercana (sin cruzar); tras acción, 1ª acción segura (asegurar/pase simple).</t>
+  </si>
+  <si>
+    <t>E1: persigues “al hombre” sin ganar línea balón–portería (no condicionas). E2: cruzas para entrar con pierna alejada o te lanzas sin igualar altura.</t>
+  </si>
+  <si>
+    <t>Falta, te eliminan, o progresión limpia.</t>
+  </si>
+  <si>
+    <t>P9</t>
+  </si>
+  <si>
+    <t>Fijar + descargar / girar</t>
+  </si>
+  <si>
+    <t>P9 se descuelga, recibe de cara o semi-espaldas entre líneas y amenaza descarga rápida o giro.</t>
+  </si>
+  <si>
+    <t>Cuando el pase “viaja” y puedes atacar recepción (antes de que oriente 1º toque) o cuando el control no es perfecto (balón se separa).</t>
+  </si>
+  <si>
+    <t>Salto agresivo para llegar en el primer contacto, negar giro y forzar descarga peor (o robo), sosteniendo espalda/estructura.</t>
+  </si>
+  <si>
+    <t>Primer paso explosivo + carrera corta; llegada con frenada 1–2 apoyos; semiperfil (interior protegido); contacto legal hombro–pecho/brazo de referencia (sin agarrar); pie cercano listo para pinchar si balón se separa; si descarga, reaccionar a 2ª acción (anticipar línea de pase cercana); comunicación con pareja para cubrir espalda.</t>
+  </si>
+  <si>
+    <t>E1: saltas tarde (P9 orienta y descarga limpio) → progresión rival. E2: saltas sin base/espalda protegida → P9 gira o te fijan y juegan a tu espalda.</t>
+  </si>
+  <si>
+    <t>Descarga cómoda + ruptura / giro + conducción / línea rota.</t>
   </si>
 </sst>
 </file>
@@ -992,11 +1325,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.453125" customWidth="1"/>
-    <col min="4" max="5" width="26.36328125" customWidth="1"/>
+    <col min="1" max="1" width="8.6328125" customWidth="1"/>
+    <col min="2" max="2" width="5.6328125" customWidth="1"/>
+    <col min="3" max="3" width="7" customWidth="1"/>
+    <col min="4" max="4" width="15.54296875" customWidth="1"/>
+    <col min="5" max="5" width="9.6328125" customWidth="1"/>
     <col min="8" max="8" width="6.90625" customWidth="1"/>
     <col min="9" max="11" width="7" customWidth="1"/>
   </cols>
@@ -1434,10 +1770,10 @@
         <v>108</v>
       </c>
       <c r="F8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -1446,28 +1782,28 @@
         <v>38</v>
       </c>
       <c r="J8" t="s">
+        <v>142</v>
+      </c>
+      <c r="K8" t="s">
+        <v>143</v>
+      </c>
+      <c r="L8" t="s">
         <v>144</v>
       </c>
-      <c r="K8" t="s">
+      <c r="M8" t="s">
         <v>145</v>
       </c>
-      <c r="L8" t="s">
+      <c r="N8" t="s">
         <v>146</v>
       </c>
-      <c r="M8" t="s">
+      <c r="O8" t="s">
         <v>147</v>
       </c>
-      <c r="N8" t="s">
+      <c r="P8" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q8" t="s">
         <v>148</v>
-      </c>
-      <c r="O8" t="s">
-        <v>149</v>
-      </c>
-      <c r="P8" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>150</v>
       </c>
       <c r="R8" s="1" t="s">
         <v>101</v>
@@ -1496,37 +1832,37 @@
         <v>51</v>
       </c>
       <c r="G9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I9" t="s">
         <v>38</v>
       </c>
       <c r="J9" t="s">
+        <v>151</v>
+      </c>
+      <c r="K9" t="s">
+        <v>152</v>
+      </c>
+      <c r="L9" t="s">
         <v>153</v>
       </c>
-      <c r="K9" t="s">
+      <c r="M9" t="s">
         <v>154</v>
       </c>
-      <c r="L9" t="s">
+      <c r="N9" t="s">
         <v>155</v>
       </c>
-      <c r="M9" t="s">
+      <c r="O9" t="s">
         <v>156</v>
       </c>
-      <c r="N9" t="s">
+      <c r="P9" t="s">
         <v>157</v>
       </c>
-      <c r="O9" t="s">
-        <v>158</v>
-      </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>159</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>161</v>
       </c>
       <c r="R9" s="1" t="s">
         <v>106</v>
@@ -1555,7 +1891,7 @@
         <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>109</v>
+        <v>208</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -1564,34 +1900,34 @@
         <v>38</v>
       </c>
       <c r="J10" t="s">
+        <v>109</v>
+      </c>
+      <c r="K10" t="s">
         <v>110</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>111</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>112</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>113</v>
       </c>
-      <c r="N10" t="s">
+      <c r="O10" t="s">
         <v>114</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>115</v>
       </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>116</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="R10" s="1" t="s">
+      <c r="S10" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.35">
@@ -1605,13 +1941,13 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E11" t="s">
         <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G11" t="s">
         <v>19</v>
@@ -1620,37 +1956,37 @@
         <v>15</v>
       </c>
       <c r="I11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J11" t="s">
         <v>22</v>
       </c>
       <c r="K11" t="s">
+        <v>123</v>
+      </c>
+      <c r="L11" t="s">
         <v>124</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
+        <v>136</v>
+      </c>
+      <c r="N11" t="s">
+        <v>137</v>
+      </c>
+      <c r="O11" t="s">
+        <v>138</v>
+      </c>
+      <c r="P11" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>140</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="S11" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="M11" t="s">
-        <v>138</v>
-      </c>
-      <c r="N11" t="s">
-        <v>139</v>
-      </c>
-      <c r="O11" t="s">
-        <v>140</v>
-      </c>
-      <c r="P11" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>142</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
@@ -1676,40 +2012,718 @@
         <v>52</v>
       </c>
       <c r="H12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I12" t="s">
         <v>38</v>
       </c>
       <c r="J12" t="s">
+        <v>128</v>
+      </c>
+      <c r="K12" t="s">
+        <v>129</v>
+      </c>
+      <c r="L12" t="s">
         <v>130</v>
       </c>
-      <c r="K12" t="s">
+      <c r="M12" t="s">
         <v>131</v>
       </c>
-      <c r="L12" t="s">
+      <c r="N12" t="s">
         <v>132</v>
       </c>
-      <c r="M12" t="s">
+      <c r="O12" t="s">
         <v>133</v>
       </c>
-      <c r="N12" t="s">
+      <c r="P12" t="s">
         <v>134</v>
       </c>
-      <c r="O12" t="s">
+      <c r="Q12" t="s">
         <v>135</v>
       </c>
-      <c r="P12" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>137</v>
-      </c>
       <c r="R12" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>161</v>
+      </c>
+      <c r="E13" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" t="s">
+        <v>151</v>
+      </c>
+      <c r="K13" t="s">
+        <v>187</v>
+      </c>
+      <c r="L13" t="s">
+        <v>188</v>
+      </c>
+      <c r="M13" t="s">
+        <v>189</v>
+      </c>
+      <c r="N13" t="s">
+        <v>190</v>
+      </c>
+      <c r="O13" t="s">
+        <v>191</v>
+      </c>
+      <c r="P13" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>193</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>162</v>
+      </c>
+      <c r="E14" t="s">
+        <v>108</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14" t="s">
+        <v>151</v>
+      </c>
+      <c r="K14" t="s">
+        <v>194</v>
+      </c>
+      <c r="L14" t="s">
+        <v>195</v>
+      </c>
+      <c r="M14" t="s">
+        <v>196</v>
+      </c>
+      <c r="N14" t="s">
+        <v>197</v>
+      </c>
+      <c r="O14" t="s">
+        <v>198</v>
+      </c>
+      <c r="P14" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>200</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>170</v>
+      </c>
+      <c r="E15" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" t="s">
+        <v>38</v>
+      </c>
+      <c r="J15" t="s">
+        <v>151</v>
+      </c>
+      <c r="K15" t="s">
+        <v>201</v>
+      </c>
+      <c r="L15" t="s">
+        <v>202</v>
+      </c>
+      <c r="M15" t="s">
+        <v>203</v>
+      </c>
+      <c r="N15" t="s">
+        <v>204</v>
+      </c>
+      <c r="O15" t="s">
+        <v>205</v>
+      </c>
+      <c r="P15" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>207</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E16" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" t="s">
+        <v>150</v>
+      </c>
+      <c r="I16" t="s">
+        <v>38</v>
+      </c>
+      <c r="J16" t="s">
+        <v>151</v>
+      </c>
+      <c r="K16" t="s">
+        <v>209</v>
+      </c>
+      <c r="L16" t="s">
+        <v>210</v>
+      </c>
+      <c r="M16" t="s">
+        <v>211</v>
+      </c>
+      <c r="N16" t="s">
+        <v>212</v>
+      </c>
+      <c r="O16" t="s">
+        <v>213</v>
+      </c>
+      <c r="P16" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>215</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>172</v>
+      </c>
+      <c r="E17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" t="s">
+        <v>150</v>
+      </c>
+      <c r="I17" t="s">
+        <v>38</v>
+      </c>
+      <c r="J17" t="s">
+        <v>151</v>
+      </c>
+      <c r="K17" t="s">
+        <v>216</v>
+      </c>
+      <c r="L17" t="s">
+        <v>217</v>
+      </c>
+      <c r="M17" t="s">
+        <v>218</v>
+      </c>
+      <c r="N17" t="s">
+        <v>219</v>
+      </c>
+      <c r="O17" t="s">
+        <v>220</v>
+      </c>
+      <c r="P17" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>222</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>164</v>
+      </c>
+      <c r="E18" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" t="s">
+        <v>80</v>
+      </c>
+      <c r="I18" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18" t="s">
         <v>128</v>
       </c>
-      <c r="S12" t="s">
-        <v>129</v>
+      <c r="K18" t="s">
+        <v>223</v>
+      </c>
+      <c r="L18" t="s">
+        <v>224</v>
+      </c>
+      <c r="M18" t="s">
+        <v>225</v>
+      </c>
+      <c r="N18" t="s">
+        <v>226</v>
+      </c>
+      <c r="O18" t="s">
+        <v>227</v>
+      </c>
+      <c r="P18" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>229</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19" t="s">
+        <v>149</v>
+      </c>
+      <c r="H19" t="s">
+        <v>150</v>
+      </c>
+      <c r="I19" t="s">
+        <v>38</v>
+      </c>
+      <c r="J19" t="s">
+        <v>151</v>
+      </c>
+      <c r="K19" t="s">
+        <v>152</v>
+      </c>
+      <c r="L19" t="s">
+        <v>230</v>
+      </c>
+      <c r="M19" t="s">
+        <v>154</v>
+      </c>
+      <c r="N19" t="s">
+        <v>155</v>
+      </c>
+      <c r="O19" t="s">
+        <v>156</v>
+      </c>
+      <c r="P19" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>159</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
+        <v>166</v>
+      </c>
+      <c r="E20" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>232</v>
+      </c>
+      <c r="H20" t="s">
+        <v>233</v>
+      </c>
+      <c r="I20" t="s">
+        <v>38</v>
+      </c>
+      <c r="J20" t="s">
+        <v>151</v>
+      </c>
+      <c r="K20" t="s">
+        <v>234</v>
+      </c>
+      <c r="L20" t="s">
+        <v>235</v>
+      </c>
+      <c r="M20" t="s">
+        <v>236</v>
+      </c>
+      <c r="N20" t="s">
+        <v>237</v>
+      </c>
+      <c r="O20" t="s">
+        <v>238</v>
+      </c>
+      <c r="P20" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>240</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
+        <v>163</v>
+      </c>
+      <c r="E21" t="s">
+        <v>108</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" t="s">
+        <v>38</v>
+      </c>
+      <c r="J21" t="s">
+        <v>241</v>
+      </c>
+      <c r="K21" t="s">
+        <v>242</v>
+      </c>
+      <c r="L21" t="s">
+        <v>243</v>
+      </c>
+      <c r="M21" t="s">
+        <v>244</v>
+      </c>
+      <c r="N21" t="s">
+        <v>245</v>
+      </c>
+      <c r="O21" t="s">
+        <v>246</v>
+      </c>
+      <c r="P21" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>248</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>167</v>
+      </c>
+      <c r="E22" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>249</v>
+      </c>
+      <c r="H22" t="s">
+        <v>233</v>
+      </c>
+      <c r="I22" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" t="s">
+        <v>253</v>
+      </c>
+      <c r="L22" t="s">
+        <v>250</v>
+      </c>
+      <c r="M22" t="s">
+        <v>251</v>
+      </c>
+      <c r="N22" t="s">
+        <v>252</v>
+      </c>
+      <c r="O22" t="s">
+        <v>254</v>
+      </c>
+      <c r="P22" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>256</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" t="s">
+        <v>168</v>
+      </c>
+      <c r="E23" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" t="s">
+        <v>126</v>
+      </c>
+      <c r="I23" t="s">
+        <v>122</v>
+      </c>
+      <c r="J23" t="s">
+        <v>257</v>
+      </c>
+      <c r="K23" t="s">
+        <v>258</v>
+      </c>
+      <c r="L23" t="s">
+        <v>259</v>
+      </c>
+      <c r="M23" t="s">
+        <v>260</v>
+      </c>
+      <c r="N23" t="s">
+        <v>261</v>
+      </c>
+      <c r="O23" t="s">
+        <v>262</v>
+      </c>
+      <c r="P23" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>264</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
+        <v>169</v>
+      </c>
+      <c r="E24" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24" t="s">
+        <v>80</v>
+      </c>
+      <c r="I24" t="s">
+        <v>38</v>
+      </c>
+      <c r="J24" t="s">
+        <v>265</v>
+      </c>
+      <c r="K24" t="s">
+        <v>266</v>
+      </c>
+      <c r="L24" t="s">
+        <v>267</v>
+      </c>
+      <c r="M24" t="s">
+        <v>268</v>
+      </c>
+      <c r="N24" t="s">
+        <v>269</v>
+      </c>
+      <c r="O24" t="s">
+        <v>270</v>
+      </c>
+      <c r="P24" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>272</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -1736,6 +2750,21 @@
     <hyperlink ref="R11" r:id="rId19" xr:uid="{2C7EE011-32B3-424E-8458-51C4C555B670}"/>
     <hyperlink ref="S11" r:id="rId20" xr:uid="{ACEB8A79-91C3-417D-9CCE-64F1B16F6B26}"/>
     <hyperlink ref="R12" r:id="rId21" xr:uid="{811E8F14-5351-453D-A446-D38C34CAF783}"/>
+    <hyperlink ref="S12" r:id="rId22" xr:uid="{6B86807A-E884-432B-AFFB-3998160073C1}"/>
+    <hyperlink ref="R13" r:id="rId23" xr:uid="{67768D6D-F513-4699-8DCE-F2E29BC612B1}"/>
+    <hyperlink ref="R14" r:id="rId24" xr:uid="{E01E9906-314A-440E-92BE-578C169EDB0F}"/>
+    <hyperlink ref="R15" r:id="rId25" xr:uid="{3B04F34A-431C-490C-A183-82108C902B82}"/>
+    <hyperlink ref="R16" r:id="rId26" xr:uid="{1523C1D6-0D2F-4E53-B47A-6CF14FC88286}"/>
+    <hyperlink ref="R17" r:id="rId27" xr:uid="{E5DDF90A-6BD8-46B7-BD4B-5DBC7ABF1CD2}"/>
+    <hyperlink ref="R18" r:id="rId28" xr:uid="{4A9CC67C-E965-4139-B592-3F09A5F1B27E}"/>
+    <hyperlink ref="R24" r:id="rId29" xr:uid="{AA925232-3A7A-4D21-ABB9-D97B42405E57}"/>
+    <hyperlink ref="R19" r:id="rId30" xr:uid="{C5285491-1BA4-46F1-91E0-4DCA716CA2D1}"/>
+    <hyperlink ref="S19" r:id="rId31" xr:uid="{048546BC-4644-485C-9B49-117EA039EFBE}"/>
+    <hyperlink ref="R20" r:id="rId32" xr:uid="{7619AC58-528F-42FA-8580-4036F367545B}"/>
+    <hyperlink ref="R21" r:id="rId33" xr:uid="{37BE137D-1F39-444E-885F-B85C917A1C22}"/>
+    <hyperlink ref="S21" r:id="rId34" xr:uid="{C76FE405-9F66-46B9-97BF-F00BF01BCC4A}"/>
+    <hyperlink ref="R22" r:id="rId35" xr:uid="{3894148D-7AA2-4FFD-B2F1-AB3B81170D10}"/>
+    <hyperlink ref="R23" r:id="rId36" xr:uid="{E13B0534-2413-4D79-AD8A-8F7EE8E08E78}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/conductas_micro.xlsx
+++ b/conductas_micro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\losaa\Downloads\Escritorio\Conductas Micro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04BDECD-8F6A-4988-80C6-DE965C0265C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF33089-DF02-4317-8BB4-67522B5698FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19290" yWindow="-4840" windowWidth="19380" windowHeight="20970" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-4950" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="P1" sheetId="2" r:id="rId1"/>
@@ -553,9 +553,6 @@
     <t>Defensa 1c1 - Uso funcional del brazo</t>
   </si>
   <si>
-    <t>https://youtu.be/EfVRM0Kq-Va</t>
-  </si>
-  <si>
     <t>https://youtu.be/Wg7aI4TtuPA</t>
   </si>
   <si>
@@ -851,6 +848,9 @@
   </si>
   <si>
     <t>Descarga cómoda + ruptura / giro + conducción / línea rota.</t>
+  </si>
+  <si>
+    <t>https://youtu.be/EfVRM0Kq-vA</t>
   </si>
 </sst>
 </file>
@@ -1891,7 +1891,7 @@
         <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -2080,28 +2080,28 @@
         <v>151</v>
       </c>
       <c r="K13" t="s">
+        <v>186</v>
+      </c>
+      <c r="L13" t="s">
         <v>187</v>
       </c>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
         <v>188</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>189</v>
       </c>
-      <c r="N13" t="s">
+      <c r="O13" t="s">
         <v>190</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>191</v>
       </c>
-      <c r="P13" t="s">
+      <c r="Q13" t="s">
         <v>192</v>
       </c>
-      <c r="Q13" t="s">
-        <v>193</v>
-      </c>
       <c r="R13" s="1" t="s">
-        <v>173</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
@@ -2136,28 +2136,28 @@
         <v>151</v>
       </c>
       <c r="K14" t="s">
+        <v>193</v>
+      </c>
+      <c r="L14" t="s">
         <v>194</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>195</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>196</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
         <v>197</v>
       </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
         <v>198</v>
       </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
         <v>199</v>
       </c>
-      <c r="Q14" t="s">
-        <v>200</v>
-      </c>
       <c r="R14" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.35">
@@ -2192,28 +2192,28 @@
         <v>151</v>
       </c>
       <c r="K15" t="s">
+        <v>200</v>
+      </c>
+      <c r="L15" t="s">
         <v>201</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>202</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>203</v>
       </c>
-      <c r="N15" t="s">
+      <c r="O15" t="s">
         <v>204</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
         <v>205</v>
       </c>
-      <c r="P15" t="s">
+      <c r="Q15" t="s">
         <v>206</v>
       </c>
-      <c r="Q15" t="s">
-        <v>207</v>
-      </c>
       <c r="R15" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.35">
@@ -2248,28 +2248,28 @@
         <v>151</v>
       </c>
       <c r="K16" t="s">
+        <v>208</v>
+      </c>
+      <c r="L16" t="s">
         <v>209</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
         <v>210</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>211</v>
       </c>
-      <c r="N16" t="s">
+      <c r="O16" t="s">
         <v>212</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>213</v>
       </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
         <v>214</v>
       </c>
-      <c r="Q16" t="s">
-        <v>215</v>
-      </c>
       <c r="R16" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.35">
@@ -2304,28 +2304,28 @@
         <v>151</v>
       </c>
       <c r="K17" t="s">
+        <v>215</v>
+      </c>
+      <c r="L17" t="s">
         <v>216</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>217</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>218</v>
       </c>
-      <c r="N17" t="s">
+      <c r="O17" t="s">
         <v>219</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>220</v>
       </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
         <v>221</v>
       </c>
-      <c r="Q17" t="s">
-        <v>222</v>
-      </c>
       <c r="R17" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.35">
@@ -2360,28 +2360,28 @@
         <v>128</v>
       </c>
       <c r="K18" t="s">
+        <v>222</v>
+      </c>
+      <c r="L18" t="s">
         <v>223</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
         <v>224</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>225</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>226</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>227</v>
       </c>
-      <c r="P18" t="s">
+      <c r="Q18" t="s">
         <v>228</v>
       </c>
-      <c r="Q18" t="s">
-        <v>229</v>
-      </c>
       <c r="R18" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.35">
@@ -2419,7 +2419,7 @@
         <v>152</v>
       </c>
       <c r="L19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M19" t="s">
         <v>154</v>
@@ -2431,16 +2431,16 @@
         <v>156</v>
       </c>
       <c r="P19" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q19" t="s">
         <v>159</v>
       </c>
       <c r="R19" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="S19" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.35">
@@ -2463,10 +2463,10 @@
         <v>18</v>
       </c>
       <c r="G20" t="s">
+        <v>231</v>
+      </c>
+      <c r="H20" t="s">
         <v>232</v>
-      </c>
-      <c r="H20" t="s">
-        <v>233</v>
       </c>
       <c r="I20" t="s">
         <v>38</v>
@@ -2475,28 +2475,28 @@
         <v>151</v>
       </c>
       <c r="K20" t="s">
+        <v>233</v>
+      </c>
+      <c r="L20" t="s">
         <v>234</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>235</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>236</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O20" t="s">
         <v>237</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>238</v>
       </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
         <v>239</v>
       </c>
-      <c r="Q20" t="s">
-        <v>240</v>
-      </c>
       <c r="R20" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.35">
@@ -2528,34 +2528,34 @@
         <v>38</v>
       </c>
       <c r="J21" t="s">
+        <v>240</v>
+      </c>
+      <c r="K21" t="s">
         <v>241</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>242</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
         <v>243</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>244</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>245</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>246</v>
       </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
         <v>247</v>
       </c>
-      <c r="Q21" t="s">
-        <v>248</v>
-      </c>
       <c r="R21" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="S21" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.35">
@@ -2578,10 +2578,10 @@
         <v>18</v>
       </c>
       <c r="G22" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I22" t="s">
         <v>20</v>
@@ -2590,28 +2590,28 @@
         <v>22</v>
       </c>
       <c r="K22" t="s">
+        <v>252</v>
+      </c>
+      <c r="L22" t="s">
+        <v>249</v>
+      </c>
+      <c r="M22" t="s">
+        <v>250</v>
+      </c>
+      <c r="N22" t="s">
+        <v>251</v>
+      </c>
+      <c r="O22" t="s">
         <v>253</v>
       </c>
-      <c r="L22" t="s">
-        <v>250</v>
-      </c>
-      <c r="M22" t="s">
-        <v>251</v>
-      </c>
-      <c r="N22" t="s">
-        <v>252</v>
-      </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>254</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>255</v>
       </c>
-      <c r="Q22" t="s">
-        <v>256</v>
-      </c>
       <c r="R22" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.35">
@@ -2643,31 +2643,31 @@
         <v>122</v>
       </c>
       <c r="J23" t="s">
+        <v>256</v>
+      </c>
+      <c r="K23" t="s">
         <v>257</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>258</v>
       </c>
-      <c r="L23" t="s">
+      <c r="M23" t="s">
         <v>259</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>260</v>
       </c>
-      <c r="N23" t="s">
+      <c r="O23" t="s">
         <v>261</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>262</v>
       </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
         <v>263</v>
       </c>
-      <c r="Q23" t="s">
-        <v>264</v>
-      </c>
       <c r="R23" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.35">
@@ -2699,31 +2699,31 @@
         <v>38</v>
       </c>
       <c r="J24" t="s">
+        <v>264</v>
+      </c>
+      <c r="K24" t="s">
         <v>265</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>266</v>
       </c>
-      <c r="L24" t="s">
+      <c r="M24" t="s">
         <v>267</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" t="s">
         <v>268</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
         <v>269</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>270</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>271</v>
       </c>
-      <c r="Q24" t="s">
-        <v>272</v>
-      </c>
       <c r="R24" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/conductas_micro.xlsx
+++ b/conductas_micro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\losaa\Downloads\Escritorio\Conductas Micro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF33089-DF02-4317-8BB4-67522B5698FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFCD71CB-986C-4D39-9690-361A3904CD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-4950" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -850,7 +850,7 @@
     <t>Descarga cómoda + ruptura / giro + conducción / línea rota.</t>
   </si>
   <si>
-    <t>https://youtu.be/EfVRM0Kq-vA</t>
+    <t>https://youtu.be/EfVRM0Kq-vA?si=fWKziC61rzMe4Jhz</t>
   </si>
 </sst>
 </file>

--- a/conductas_micro.xlsx
+++ b/conductas_micro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\losaa\Downloads\Escritorio\Conductas Micro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFCD71CB-986C-4D39-9690-361A3904CD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA0ECD1-C656-48AE-8313-806A525C04EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-4950" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -850,7 +850,7 @@
     <t>Descarga cómoda + ruptura / giro + conducción / línea rota.</t>
   </si>
   <si>
-    <t>https://youtu.be/EfVRM0Kq-vA?si=fWKziC61rzMe4Jhz</t>
+    <t>https://youtu.be/r01k2HCxzZc</t>
   </si>
 </sst>
 </file>

--- a/conductas_micro.xlsx
+++ b/conductas_micro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\losaa\Downloads\Escritorio\Conductas Micro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA0ECD1-C656-48AE-8313-806A525C04EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1482EF32-345C-4682-B115-F9C933A04ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-4950" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/conductas_micro.xlsx
+++ b/conductas_micro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\losaa\Downloads\Escritorio\Conductas Micro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1482EF32-345C-4682-B115-F9C933A04ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671365BF-7F14-4238-B0E9-2FF21B53FA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-4950" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
